--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -868,7 +868,7 @@
     <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
   </si>
   <si>
-    <t>planned</t>
+    <t>finished</t>
   </si>
   <si>
     <t>Current state of the encounter.</t>
@@ -3241,7 +3241,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>139</v>
       </c>
@@ -3251,13 +3251,13 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>76</v>
@@ -3335,7 +3335,7 @@
         <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>143</v>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1377,7 +1377,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/CondicionInicio1LE)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioDiagnosticoSospechaLE)
 </t>
   </si>
   <si>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1079,7 +1079,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>
@@ -7339,7 +7339,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>343</v>
       </c>
@@ -7349,13 +7349,13 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="512">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -579,371 +579,193 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>Encounter.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding</t>
+    <t>Encounter.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Encounter.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Encounter.status</t>
+  </si>
+  <si>
+    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +</t>
+  </si>
+  <si>
+    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
+  </si>
+  <si>
+    <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
+  </si>
+  <si>
+    <t>finished</t>
+  </si>
+  <si>
+    <t>Current state of the encounter.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>List of past encounter statuses</t>
+  </si>
+  <si>
+    <t>The status history permits the encounter resource to contain the status history without needing to read through the historical versions of the resource, or even have the server store them.</t>
+  </si>
+  <si>
+    <t>The current status is always found in the current version of the resource, not the status history.</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.id</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.extension</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.status</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.period</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified status</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified status.</t>
+  </si>
+  <si>
+    <t>Encounter.class</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>IdConsultaAPS</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>Encounter.status</t>
-  </si>
-  <si>
-    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +</t>
-  </si>
-  <si>
-    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
-  </si>
-  <si>
-    <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
-  </si>
-  <si>
-    <t>finished</t>
-  </si>
-  <si>
-    <t>Current state of the encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>List of past encounter statuses</t>
-  </si>
-  <si>
-    <t>The status history permits the encounter resource to contain the status history without needing to read through the historical versions of the resource, or even have the server store them.</t>
-  </si>
-  <si>
-    <t>The current status is always found in the current version of the resource, not the status history.</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.id</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.status</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.period</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified status</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified status.</t>
-  </si>
-  <si>
-    <t>Encounter.class</t>
   </si>
   <si>
     <t>Classification of patient encounter</t>
@@ -2084,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM93"/>
+  <dimension ref="A1:AM82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
@@ -3686,7 +3508,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>170</v>
       </c>
@@ -3696,13 +3518,13 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3821,19 +3643,23 @@
         <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3845,7 +3671,7 @@
         <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>77</v>
@@ -3881,7 +3707,7 @@
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>75</v>
@@ -3893,56 +3719,56 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -3956,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3980,48 +3806,48 @@
         <v>77</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -4029,13 +3855,13 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -4044,20 +3870,16 @@
         <v>84</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
         <v>77</v>
       </c>
@@ -4105,13 +3927,13 @@
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>77</v>
@@ -4123,18 +3945,18 @@
         <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -4154,18 +3976,20 @@
         <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M19" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
         <v>77</v>
@@ -4214,7 +4038,7 @@
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>75</v>
@@ -4226,56 +4050,56 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>130</v>
+        <v>214</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
@@ -4286,7 +4110,7 @@
         <v>77</v>
       </c>
       <c r="R20" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>77</v>
@@ -4301,60 +4125,60 @@
         <v>77</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AC20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>159</v>
+        <v>213</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -4362,35 +4186,33 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4438,13 +4260,13 @@
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>77</v>
@@ -4456,18 +4278,18 @@
         <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4487,20 +4309,18 @@
         <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>149</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>77</v>
@@ -4549,7 +4369,7 @@
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>75</v>
@@ -4561,58 +4381,58 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4621,7 +4441,7 @@
         <v>77</v>
       </c>
       <c r="R23" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>77</v>
@@ -4660,69 +4480,71 @@
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M24" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N24" t="s" s="2">
-        <v>220</v>
+        <v>138</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>77</v>
@@ -4771,36 +4593,36 @@
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4808,7 +4630,7 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>83</v>
@@ -4820,23 +4642,19 @@
         <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4860,13 +4678,13 @@
         <v>77</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>77</v>
@@ -4884,10 +4702,10 @@
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -4902,18 +4720,18 @@
         <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4921,7 +4739,7 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>83</v>
@@ -4933,23 +4751,19 @@
         <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4997,10 +4811,10 @@
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5015,18 +4829,18 @@
         <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>239</v>
+        <v>153</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5034,7 +4848,7 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>83</v>
@@ -5049,7 +4863,7 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>97</v>
+        <v>241</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>242</v>
@@ -5057,12 +4871,8 @@
       <c r="L27" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>245</v>
-      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>77</v>
       </c>
@@ -5074,7 +4884,7 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>77</v>
@@ -5086,13 +4896,13 @@
         <v>77</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>77</v>
@@ -5110,10 +4920,10 @@
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5128,18 +4938,18 @@
         <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
         <v>249</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5147,32 +4957,30 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>77</v>
@@ -5185,7 +4993,7 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>77</v>
@@ -5221,13 +5029,13 @@
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>77</v>
@@ -5239,18 +5047,18 @@
         <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5270,16 +5078,16 @@
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>259</v>
+        <v>149</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>151</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -5330,7 +5138,7 @@
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>262</v>
+        <v>152</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>75</v>
@@ -5342,35 +5150,35 @@
         <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>77</v>
@@ -5379,19 +5187,19 @@
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>266</v>
+        <v>129</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>267</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>132</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
@@ -5441,50 +5249,50 @@
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>270</v>
+        <v>159</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -5493,18 +5301,20 @@
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5513,7 +5323,7 @@
         <v>77</v>
       </c>
       <c r="R31" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>77</v>
@@ -5528,13 +5338,13 @@
         <v>77</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>77</v>
@@ -5552,36 +5362,36 @@
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>281</v>
+        <v>126</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5589,10 +5399,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>77</v>
@@ -5604,17 +5414,15 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>77</v>
@@ -5639,13 +5447,13 @@
         <v>77</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>77</v>
@@ -5663,13 +5471,13 @@
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>77</v>
@@ -5692,7 +5500,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5700,7 +5508,7 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>83</v>
@@ -5715,13 +5523,13 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5772,10 +5580,10 @@
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -5784,7 +5592,7 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>77</v>
@@ -5801,11 +5609,11 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5821,19 +5629,19 @@
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>132</v>
+        <v>264</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
@@ -5859,13 +5667,13 @@
         <v>77</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>77</v>
@@ -5883,7 +5691,7 @@
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>159</v>
+        <v>261</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>75</v>
@@ -5895,60 +5703,56 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>153</v>
+        <v>269</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5972,13 +5776,13 @@
         <v>77</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>77</v>
@@ -5996,36 +5800,36 @@
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6033,7 +5837,7 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>83</v>
@@ -6048,13 +5852,13 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -6081,13 +5885,13 @@
         <v>77</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>77</v>
@@ -6105,10 +5909,10 @@
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6123,22 +5927,22 @@
         <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6148,24 +5952,26 @@
         <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>77</v>
@@ -6214,10 +6020,10 @@
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6229,21 +6035,21 @@
         <v>95</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6251,10 +6057,10 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>77</v>
@@ -6266,13 +6072,13 @@
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6299,13 +6105,13 @@
         <v>77</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>77</v>
@@ -6323,13 +6129,13 @@
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>77</v>
@@ -6338,25 +6144,25 @@
         <v>95</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6375,13 +6181,13 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -6432,7 +6238,7 @@
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>75</v>
@@ -6447,10 +6253,10 @@
         <v>95</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>153</v>
+        <v>307</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -6461,7 +6267,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6472,7 +6278,7 @@
         <v>75</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>77</v>
@@ -6481,16 +6287,16 @@
         <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>150</v>
+        <v>309</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6541,47 +6347,47 @@
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>153</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>77</v>
@@ -6593,17 +6399,15 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
         <v>77</v>
@@ -6652,19 +6456,19 @@
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>77</v>
@@ -6681,11 +6485,11 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>292</v>
+        <v>128</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6698,26 +6502,24 @@
         <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>129</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>293</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>294</v>
+        <v>155</v>
       </c>
       <c r="M42" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6765,7 +6567,7 @@
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>295</v>
+        <v>159</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>75</v>
@@ -6783,7 +6585,7 @@
         <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6794,39 +6596,43 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6850,13 +6656,13 @@
         <v>77</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>77</v>
@@ -6874,25 +6680,25 @@
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>314</v>
+        <v>235</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6911,10 +6717,10 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>77</v>
@@ -6923,10 +6729,10 @@
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>318</v>
@@ -6934,7 +6740,9 @@
       <c r="L44" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>77</v>
@@ -6959,13 +6767,13 @@
         <v>77</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>77</v>
@@ -6986,10 +6794,10 @@
         <v>317</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>77</v>
@@ -6998,21 +6806,21 @@
         <v>95</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>153</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7023,7 +6831,7 @@
         <v>75</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>77</v>
@@ -7032,20 +6840,18 @@
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>77</v>
@@ -7070,37 +6876,37 @@
         <v>77</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y45" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AF45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>77</v>
@@ -7109,13 +6915,13 @@
         <v>95</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>328</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>329</v>
@@ -7146,13 +6952,13 @@
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>171</v>
+        <v>331</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7179,13 +6985,13 @@
         <v>77</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>77</v>
@@ -7218,21 +7024,21 @@
         <v>95</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>153</v>
+        <v>335</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7240,28 +7046,28 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7288,37 +7094,37 @@
         <v>77</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Y47" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AF47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>77</v>
@@ -7327,53 +7133,53 @@
         <v>95</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>344</v>
+        <v>77</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
@@ -7423,7 +7229,7 @@
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>75</v>
@@ -7438,21 +7244,21 @@
         <v>95</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AK48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7463,7 +7269,7 @@
         <v>75</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>77</v>
@@ -7472,18 +7278,20 @@
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="K49" t="s" s="2">
+      <c r="L49" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>77</v>
@@ -7532,13 +7340,13 @@
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>77</v>
@@ -7547,25 +7355,25 @@
         <v>95</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AK49" t="s" s="2">
-        <v>153</v>
-      </c>
       <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7581,18 +7389,20 @@
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="K50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
         <v>77</v>
@@ -7617,13 +7427,13 @@
         <v>77</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>77</v>
@@ -7641,7 +7451,7 @@
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>75</v>
@@ -7656,25 +7466,25 @@
         <v>95</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7693,15 +7503,17 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M51" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
         <v>77</v>
@@ -7750,7 +7562,7 @@
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>75</v>
@@ -7765,16 +7577,16 @@
         <v>95</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -7790,7 +7602,7 @@
         <v>75</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>77</v>
@@ -7799,16 +7611,16 @@
         <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>150</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>151</v>
+        <v>375</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -7859,25 +7671,25 @@
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>152</v>
+        <v>373</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>153</v>
+        <v>376</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
@@ -7888,18 +7700,18 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>77</v>
@@ -7911,17 +7723,15 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>77</v>
@@ -7970,19 +7780,19 @@
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>77</v>
@@ -7999,11 +7809,11 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>292</v>
+        <v>128</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8016,26 +7826,24 @@
         <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>129</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>293</v>
+        <v>130</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>294</v>
+        <v>155</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8083,7 +7891,7 @@
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>295</v>
+        <v>159</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>75</v>
@@ -8101,7 +7909,7 @@
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
@@ -8112,11 +7920,11 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8129,24 +7937,26 @@
         <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>377</v>
+        <v>233</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>378</v>
+        <v>234</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8170,13 +7980,13 @@
         <v>77</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>380</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>77</v>
@@ -8194,7 +8004,7 @@
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>376</v>
+        <v>235</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>75</v>
@@ -8206,32 +8016,32 @@
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>382</v>
+        <v>126</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>83</v>
@@ -8243,18 +8053,20 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M56" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>77</v>
@@ -8303,10 +8115,10 @@
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -8318,21 +8130,21 @@
         <v>95</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8352,16 +8164,16 @@
         <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8388,13 +8200,13 @@
         <v>77</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>77</v>
@@ -8412,7 +8224,7 @@
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>75</v>
@@ -8427,21 +8239,21 @@
         <v>95</v>
       </c>
       <c r="AJ57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8449,28 +8261,28 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -8521,13 +8333,13 @@
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>77</v>
@@ -8536,21 +8348,21 @@
         <v>95</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8561,7 +8373,7 @@
         <v>75</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>77</v>
@@ -8573,16 +8385,16 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>259</v>
+        <v>399</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -8632,13 +8444,13 @@
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>77</v>
@@ -8647,21 +8459,21 @@
         <v>95</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>410</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8684,16 +8496,16 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>412</v>
+        <v>225</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
@@ -8743,7 +8555,7 @@
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>75</v>
@@ -8758,32 +8570,32 @@
         <v>95</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>417</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>77</v>
@@ -8792,20 +8604,18 @@
         <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
         <v>77</v>
@@ -8830,13 +8640,13 @@
         <v>77</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>423</v>
+        <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>77</v>
@@ -8854,40 +8664,40 @@
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>418</v>
+        <v>152</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>426</v>
+        <v>153</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>428</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>419</v>
+        <v>128</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8903,19 +8713,19 @@
         <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>430</v>
+        <v>129</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>431</v>
+        <v>130</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>421</v>
+        <v>155</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>422</v>
+        <v>132</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
@@ -8965,7 +8775,7 @@
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>429</v>
+        <v>159</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>75</v>
@@ -8977,28 +8787,28 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>426</v>
+        <v>153</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>428</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9011,22 +8821,26 @@
         <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>285</v>
+        <v>129</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9074,7 +8888,7 @@
         <v>77</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>432</v>
+        <v>235</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>75</v>
@@ -9086,13 +8900,13 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>435</v>
+        <v>126</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>77</v>
@@ -9103,7 +8917,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9126,13 +8940,13 @@
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>151</v>
+        <v>414</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -9183,7 +8997,7 @@
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>75</v>
@@ -9195,35 +9009,35 @@
         <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>77</v>
@@ -9235,17 +9049,15 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>129</v>
+        <v>417</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>418</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>77</v>
@@ -9294,25 +9106,25 @@
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>159</v>
+        <v>416</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>153</v>
+        <v>420</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>77</v>
@@ -9323,43 +9135,39 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>293</v>
+        <v>422</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9383,13 +9191,13 @@
         <v>77</v>
       </c>
       <c r="W66" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>77</v>
@@ -9407,44 +9215,44 @@
         <v>77</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>295</v>
+        <v>421</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>126</v>
+        <v>426</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>427</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>440</v>
+        <v>77</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>83</v>
@@ -9456,20 +9264,18 @@
         <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>441</v>
+        <v>171</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
         <v>77</v>
@@ -9494,13 +9300,13 @@
         <v>77</v>
       </c>
       <c r="W67" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
+        <v>431</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>77</v>
@@ -9518,10 +9324,10 @@
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -9533,21 +9339,21 @@
         <v>95</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>444</v>
+        <v>77</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>445</v>
+        <v>153</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9558,7 +9364,7 @@
         <v>75</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>77</v>
@@ -9573,13 +9379,17 @@
         <v>171</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9603,13 +9413,13 @@
         <v>77</v>
       </c>
       <c r="W68" t="s" s="2">
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>77</v>
@@ -9627,13 +9437,13 @@
         <v>77</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>77</v>
@@ -9645,18 +9455,18 @@
         <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>153</v>
+        <v>441</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9667,7 +9477,7 @@
         <v>75</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>77</v>
@@ -9679,13 +9489,13 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>453</v>
+        <v>171</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9712,13 +9522,13 @@
         <v>77</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
+        <v>446</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>77</v>
@@ -9736,13 +9546,13 @@
         <v>77</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>77</v>
@@ -9754,18 +9564,18 @@
         <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9788,17 +9598,15 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>458</v>
+        <v>171</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>77</v>
@@ -9823,13 +9631,13 @@
         <v>77</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>77</v>
+        <v>453</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>77</v>
@@ -9847,7 +9655,7 @@
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>75</v>
@@ -9865,18 +9673,18 @@
         <v>77</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -9899,17 +9707,15 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>285</v>
+        <v>417</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>77</v>
@@ -9958,7 +9764,7 @@
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>75</v>
@@ -9976,18 +9782,18 @@
         <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>77</v>
+        <v>461</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10010,13 +9816,13 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>150</v>
+        <v>463</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>151</v>
+        <v>464</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -10043,13 +9849,13 @@
         <v>77</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>465</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>466</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>77</v>
@@ -10067,7 +9873,7 @@
         <v>77</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>152</v>
+        <v>462</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>75</v>
@@ -10079,19 +9885,19 @@
         <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>153</v>
+        <v>467</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -10100,7 +9906,7 @@
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10119,16 +9925,16 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>130</v>
+        <v>470</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>155</v>
+        <v>471</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>132</v>
+        <v>472</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
@@ -10178,7 +9984,7 @@
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>159</v>
+        <v>469</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>75</v>
@@ -10190,13 +9996,13 @@
         <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>153</v>
+        <v>473</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>77</v>
@@ -10207,43 +10013,39 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>293</v>
+        <v>150</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10291,25 +10093,25 @@
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>77</v>
@@ -10320,18 +10122,18 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>77</v>
@@ -10343,15 +10145,17 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>472</v>
+        <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="M75" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
         <v>77</v>
@@ -10400,68 +10204,72 @@
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>471</v>
+        <v>159</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>474</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>476</v>
+        <v>129</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>477</v>
+        <v>233</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10509,25 +10317,25 @@
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>475</v>
+        <v>235</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>479</v>
+        <v>126</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>77</v>
@@ -10538,7 +10346,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10546,7 +10354,7 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>83</v>
@@ -10561,13 +10369,13 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>171</v>
+        <v>478</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10594,13 +10402,13 @@
         <v>77</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>483</v>
+        <v>77</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>484</v>
+        <v>77</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>77</v>
@@ -10618,10 +10426,10 @@
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -10633,21 +10441,21 @@
         <v>95</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>482</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10670,15 +10478,17 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M78" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>77</v>
@@ -10703,13 +10513,13 @@
         <v>77</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>77</v>
@@ -10727,7 +10537,7 @@
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>75</v>
@@ -10745,18 +10555,18 @@
         <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>153</v>
+        <v>490</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>492</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -10767,7 +10577,7 @@
         <v>75</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>77</v>
@@ -10782,17 +10592,15 @@
         <v>171</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L79" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>497</v>
-      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10816,13 +10624,13 @@
         <v>77</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>77</v>
@@ -10840,13 +10648,13 @@
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>77</v>
@@ -10858,18 +10666,18 @@
         <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>500</v>
+        <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>501</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -10880,7 +10688,7 @@
         <v>75</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>77</v>
@@ -10892,13 +10700,13 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -10925,13 +10733,13 @@
         <v>77</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>506</v>
+        <v>77</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>77</v>
@@ -10949,13 +10757,13 @@
         <v>77</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>77</v>
@@ -10967,18 +10775,18 @@
         <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>507</v>
+        <v>328</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>508</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -10989,7 +10797,7 @@
         <v>75</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>77</v>
@@ -11001,13 +10809,13 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11034,13 +10842,13 @@
         <v>77</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>512</v>
+        <v>77</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>513</v>
+        <v>77</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>77</v>
@@ -11058,13 +10866,13 @@
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>77</v>
@@ -11073,21 +10881,21 @@
         <v>95</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>334</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>515</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -11110,15 +10918,17 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M82" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>77</v>
@@ -11167,7 +10977,7 @@
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>75</v>
@@ -11182,1233 +10992,20 @@
         <v>95</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>77</v>
+        <v>510</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B83" s="2"/>
-      <c r="C83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D83" s="2"/>
-      <c r="E83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P83" s="2"/>
-      <c r="Q83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B84" s="2"/>
-      <c r="C84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D84" s="2"/>
-      <c r="E84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P84" s="2"/>
-      <c r="Q84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B85" s="2"/>
-      <c r="C85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P85" s="2"/>
-      <c r="Q85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="B86" s="2"/>
-      <c r="C86" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="D86" s="2"/>
-      <c r="E86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P86" s="2"/>
-      <c r="Q86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B87" s="2"/>
-      <c r="C87" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="D87" s="2"/>
-      <c r="E87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P87" s="2"/>
-      <c r="Q87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B88" s="2"/>
-      <c r="C88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D88" s="2"/>
-      <c r="E88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="F88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P88" s="2"/>
-      <c r="Q88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B89" s="2"/>
-      <c r="C89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D89" s="2"/>
-      <c r="E89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P89" s="2"/>
-      <c r="Q89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B90" s="2"/>
-      <c r="C90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D90" s="2"/>
-      <c r="E90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F90" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P90" s="2"/>
-      <c r="Q90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B91" s="2"/>
-      <c r="C91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P91" s="2"/>
-      <c r="Q91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B92" s="2"/>
-      <c r="C92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D92" s="2"/>
-      <c r="E92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P92" s="2"/>
-      <c r="Q92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B93" s="2"/>
-      <c r="C93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P93" s="2"/>
-      <c r="Q93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM93">
+  <autoFilter ref="A1:AM82">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12418,7 +11015,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-EncounterInicioLE.xlsx
+++ b/StructureDefinition-EncounterInicioLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
